--- a/sheets/조재수대금교본/검수/울어라 열풍아.xlsx
+++ b/sheets/조재수대금교본/검수/울어라 열풍아.xlsx
@@ -2661,7 +2661,7 @@
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∽</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -2682,14 +2682,13 @@
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林ʒ</t>
+林</t>
         </is>
       </c>
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃
-ㄴ</t>
+          <t xml:space="preserve">黃</t>
         </is>
       </c>
       <c r="I4" s="23"/>
@@ -2754,15 +2753,11 @@
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林仲
-林ʒ</t>
+林</t>
         </is>
       </c>
       <c r="I6" s="22"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J6" s="21"/>
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
@@ -2825,15 +2820,14 @@
       <c r="C8" s="24"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ʒ
-汰ㅅ</t>
+          <t xml:space="preserve">㳞
+汰</t>
         </is>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-ㄴ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="G8" s="24"/>
@@ -2848,8 +2842,7 @@
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-ㄴ</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="M8" s="24"/>
@@ -2858,8 +2851,7 @@
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="C9" s="22"/>
@@ -2871,8 +2863,8 @@
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ʒ
-汰⌝</t>
+          <t xml:space="preserve">㳞
+汰</t>
         </is>
       </c>
       <c r="G9" s="22"/>
@@ -2905,16 +2897,11 @@
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-㳞
-‹</t>
+㳞</t>
         </is>
       </c>
       <c r="G10" s="23"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="23"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
@@ -2974,7 +2961,7 @@
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲太∽</t>
+仲太</t>
         </is>
       </c>
       <c r="E12" s="22"/>
@@ -2989,15 +2976,14 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
-南⌝</t>
+          <t xml:space="preserve">汰
+南</t>
         </is>
       </c>
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-ㄴ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="M12" s="22"/>
@@ -3008,8 +2994,7 @@
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃∼
-‹</t>
+          <t xml:space="preserve">黃∼</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -3049,11 +3034,7 @@
         </is>
       </c>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
@@ -3066,7 +3047,7 @@
       <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ʒ
+          <t xml:space="preserve">㳞
 汰潢</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/울어라 열풍아.xlsx
+++ b/sheets/조재수대금교본/검수/울어라 열풍아.xlsx
@@ -2661,7 +2661,7 @@
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢∽</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -2682,13 +2682,14 @@
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林</t>
+林ʒ</t>
         </is>
       </c>
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃</t>
+          <t xml:space="preserve">黃
+ㄴ</t>
         </is>
       </c>
       <c r="I4" s="23"/>
@@ -2753,7 +2754,7 @@
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林仲
-林</t>
+林ʒ</t>
         </is>
       </c>
       <c r="I6" s="22"/>
@@ -2820,14 +2821,15 @@
       <c r="C8" s="24"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-汰</t>
+          <t xml:space="preserve">㳞ʒ
+汰ㅅ</t>
         </is>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+ㄴ</t>
         </is>
       </c>
       <c r="G8" s="24"/>
@@ -2842,7 +2844,8 @@
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林
+ㄴ</t>
         </is>
       </c>
       <c r="M8" s="24"/>
@@ -2863,8 +2866,8 @@
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-汰</t>
+          <t xml:space="preserve">㳞ʒ
+汰⌝</t>
         </is>
       </c>
       <c r="G9" s="22"/>
@@ -2961,7 +2964,7 @@
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲太</t>
+仲太∽</t>
         </is>
       </c>
       <c r="E12" s="22"/>
@@ -2976,14 +2979,15 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-南</t>
+          <t xml:space="preserve">汰⌝
+南⌝</t>
         </is>
       </c>
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+ㄴ</t>
         </is>
       </c>
       <c r="M12" s="22"/>
@@ -3047,7 +3051,7 @@
       <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ʒ
 汰潢</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/울어라 열풍아.xlsx
+++ b/sheets/조재수대금교본/검수/울어라 열풍아.xlsx
@@ -2595,24 +2595,24 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="56.34" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="83.81" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="83.81" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="M4" s="23"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="83.81" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="M5" s="24"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="83.81" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="M6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="83.81" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="M7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="83.81" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="M8" s="24"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="83.81" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="M9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="83.81" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
       <c r="L10" s="21"/>
       <c r="M10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="83.81" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="83.81" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="M12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="83.81" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="83.81" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3063,6 +3063,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="71"/>
 </worksheet>
 </file>